--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/102.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/102.xlsx
@@ -426,13 +426,13 @@
         <v>-10.24380504955409</v>
       </c>
       <c r="E2">
-        <v>-6.697841557752444</v>
+        <v>-8.856089627438099</v>
       </c>
       <c r="F2">
-        <v>-4.963576796454743</v>
+        <v>-4.444604618600852</v>
       </c>
       <c r="G2">
-        <v>-8.771145892963617</v>
+        <v>-9.196964812952373</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.10628975959186</v>
       </c>
       <c r="E3">
-        <v>-7.047480507410665</v>
+        <v>-8.758514597994825</v>
       </c>
       <c r="F3">
-        <v>-5.075755138509255</v>
+        <v>-4.63759434263547</v>
       </c>
       <c r="G3">
-        <v>-7.958694980534457</v>
+        <v>-8.535484708750596</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.946929155322481</v>
       </c>
       <c r="E4">
-        <v>-8.0289593214631</v>
+        <v>-9.248780779487241</v>
       </c>
       <c r="F4">
-        <v>-4.607621524899975</v>
+        <v>-4.368232457532349</v>
       </c>
       <c r="G4">
-        <v>-8.088994742414631</v>
+        <v>-9.133799604063078</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.744080481657072</v>
       </c>
       <c r="E5">
-        <v>-8.984707346203951</v>
+        <v>-9.712632372092916</v>
       </c>
       <c r="F5">
-        <v>-5.229799169101253</v>
+        <v>-4.645332950912423</v>
       </c>
       <c r="G5">
-        <v>-8.178753563620891</v>
+        <v>-8.553129916474912</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.483890571993411</v>
       </c>
       <c r="E6">
-        <v>-9.591568147971856</v>
+        <v>-11.05503962150469</v>
       </c>
       <c r="F6">
-        <v>-5.239446335874256</v>
+        <v>-4.8441991133025</v>
       </c>
       <c r="G6">
-        <v>-7.285151248387576</v>
+        <v>-8.351325681492019</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.13672814814738</v>
       </c>
       <c r="E7">
-        <v>-10.15320760829916</v>
+        <v>-11.55914481956455</v>
       </c>
       <c r="F7">
-        <v>-5.55263134168768</v>
+        <v>-4.88673412270145</v>
       </c>
       <c r="G7">
-        <v>-7.765829218507595</v>
+        <v>-8.334928549436009</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.693048532198146</v>
       </c>
       <c r="E8">
-        <v>-11.18800920379192</v>
+        <v>-12.97793836853771</v>
       </c>
       <c r="F8">
-        <v>-5.324734215299091</v>
+        <v>-4.7338290972883</v>
       </c>
       <c r="G8">
-        <v>-6.59155554190933</v>
+        <v>-7.735123908630855</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.130341826757006</v>
       </c>
       <c r="E9">
-        <v>-12.44934771151838</v>
+        <v>-13.27377904698481</v>
       </c>
       <c r="F9">
-        <v>-5.402614833408092</v>
+        <v>-4.689370618780051</v>
       </c>
       <c r="G9">
-        <v>-6.798451395931623</v>
+        <v>-7.938345057104557</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.452250273661575</v>
       </c>
       <c r="E10">
-        <v>-12.30832197397151</v>
+        <v>-13.77889862322238</v>
       </c>
       <c r="F10">
-        <v>-5.547652853596855</v>
+        <v>-5.228903703938827</v>
       </c>
       <c r="G10">
-        <v>-6.404287912389377</v>
+        <v>-7.392042142759564</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.6553777890246</v>
       </c>
       <c r="E11">
-        <v>-13.59268324355297</v>
+        <v>-14.98324628556231</v>
       </c>
       <c r="F11">
-        <v>-5.593929598554249</v>
+        <v>-4.908534267640924</v>
       </c>
       <c r="G11">
-        <v>-5.239088441114254</v>
+        <v>-6.711648891891932</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.768493865471869</v>
       </c>
       <c r="E12">
-        <v>-14.02719485306295</v>
+        <v>-15.38873037668313</v>
       </c>
       <c r="F12">
-        <v>-5.920485282616259</v>
+        <v>-5.067150886296376</v>
       </c>
       <c r="G12">
-        <v>-5.271283496483667</v>
+        <v>-5.445454607850263</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.816462461436472</v>
       </c>
       <c r="E13">
-        <v>-15.70821874639828</v>
+        <v>-16.89568425763761</v>
       </c>
       <c r="F13">
-        <v>-5.25130690034754</v>
+        <v>-5.003365767913412</v>
       </c>
       <c r="G13">
-        <v>-4.189834206261027</v>
+        <v>-5.096576076739709</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.859142386191411</v>
       </c>
       <c r="E14">
-        <v>-15.41031308380368</v>
+        <v>-16.31810456880331</v>
       </c>
       <c r="F14">
-        <v>-5.536572611217008</v>
+        <v>-4.622731774694441</v>
       </c>
       <c r="G14">
-        <v>-4.400030674185972</v>
+        <v>-4.495788203909392</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.947484493543819</v>
       </c>
       <c r="E15">
-        <v>-17.19905125988546</v>
+        <v>-17.68618373736457</v>
       </c>
       <c r="F15">
-        <v>-5.374061009033593</v>
+        <v>-4.799064686993566</v>
       </c>
       <c r="G15">
-        <v>-2.723530686552572</v>
+        <v>-3.952004614719785</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.156032370884988</v>
       </c>
       <c r="E16">
-        <v>-17.98110966406211</v>
+        <v>-18.45011918856252</v>
       </c>
       <c r="F16">
-        <v>-5.16188960941975</v>
+        <v>-4.734241624254894</v>
       </c>
       <c r="G16">
-        <v>-2.363614796614087</v>
+        <v>-3.293686081508013</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.532227408930166</v>
       </c>
       <c r="E17">
-        <v>-19.38240518946964</v>
+        <v>-19.38622722153211</v>
       </c>
       <c r="F17">
-        <v>-5.261400557150652</v>
+        <v>-4.500325580317564</v>
       </c>
       <c r="G17">
-        <v>-2.418874422755602</v>
+        <v>-2.991271057041129</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.129673399771144</v>
       </c>
       <c r="E18">
-        <v>-19.24987939763517</v>
+        <v>-20.11169781450892</v>
       </c>
       <c r="F18">
-        <v>-4.644850841083993</v>
+        <v>-3.902866419415823</v>
       </c>
       <c r="G18">
-        <v>-1.875345745572519</v>
+        <v>-3.198514518345045</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.9622926592584478</v>
       </c>
       <c r="E19">
-        <v>-20.38505461950793</v>
+        <v>-21.39076982644942</v>
       </c>
       <c r="F19">
-        <v>-4.318783065422233</v>
+        <v>-3.698217424186803</v>
       </c>
       <c r="G19">
-        <v>-1.906882002379616</v>
+        <v>-2.717435972214774</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.04445999683768</v>
       </c>
       <c r="E20">
-        <v>-21.63467343650254</v>
+        <v>-22.38488761145726</v>
       </c>
       <c r="F20">
-        <v>-3.966159487561525</v>
+        <v>-3.419105654752732</v>
       </c>
       <c r="G20">
-        <v>-2.169365226551811</v>
+        <v>-2.512162285506724</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.353190768171009</v>
       </c>
       <c r="E21">
-        <v>-21.89872422741579</v>
+        <v>-22.67557488648363</v>
       </c>
       <c r="F21">
-        <v>-3.860823460254137</v>
+        <v>-2.967590747978416</v>
       </c>
       <c r="G21">
-        <v>-2.278984010448158</v>
+        <v>-2.689372477678372</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.86895587117373</v>
       </c>
       <c r="E22">
-        <v>-22.68933239051893</v>
+        <v>-22.56093656697945</v>
       </c>
       <c r="F22">
-        <v>-3.222544838844645</v>
+        <v>-2.76020896868756</v>
       </c>
       <c r="G22">
-        <v>-2.643448589957602</v>
+        <v>-3.040353205206364</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.543080675362182</v>
       </c>
       <c r="E23">
-        <v>-23.14333002368392</v>
+        <v>-24.52896155749891</v>
       </c>
       <c r="F23">
-        <v>-3.165477780098385</v>
+        <v>-2.558335004257918</v>
       </c>
       <c r="G23">
-        <v>-2.355662866228758</v>
+        <v>-3.040680949214752</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.333372542785408</v>
       </c>
       <c r="E24">
-        <v>-23.78588878605429</v>
+        <v>-24.94731557174952</v>
       </c>
       <c r="F24">
-        <v>-2.809151399947163</v>
+        <v>-1.871948117563442</v>
       </c>
       <c r="G24">
-        <v>-3.532075155245392</v>
+        <v>-4.174066077857479</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.177934930785113</v>
       </c>
       <c r="E25">
-        <v>-24.14978790036266</v>
+        <v>-24.82466185325177</v>
       </c>
       <c r="F25">
-        <v>-2.449147068527512</v>
+        <v>-2.118275590296917</v>
       </c>
       <c r="G25">
-        <v>-3.162687794519052</v>
+        <v>-3.635215201521385</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.022948351866797</v>
       </c>
       <c r="E26">
-        <v>-24.50108427150769</v>
+        <v>-25.2140426908013</v>
       </c>
       <c r="F26">
-        <v>-2.492706768403724</v>
+        <v>-2.171278678565043</v>
       </c>
       <c r="G26">
-        <v>-3.833854554968736</v>
+        <v>-4.37996545767245</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.804743681179806</v>
       </c>
       <c r="E27">
-        <v>-24.4901706491492</v>
+        <v>-25.54377899719581</v>
       </c>
       <c r="F27">
-        <v>-2.154823160108431</v>
+        <v>-1.687744886570318</v>
       </c>
       <c r="G27">
-        <v>-4.94612502416199</v>
+        <v>-5.189801039125586</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.472074597117964</v>
       </c>
       <c r="E28">
-        <v>-24.98665442545415</v>
+        <v>-24.98965227524723</v>
       </c>
       <c r="F28">
-        <v>-2.28502097827604</v>
+        <v>-1.461870633379366</v>
       </c>
       <c r="G28">
-        <v>-4.96724961524808</v>
+        <v>-5.218910666052397</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.976791979638135</v>
       </c>
       <c r="E29">
-        <v>-24.27902602006757</v>
+        <v>-25.38777306763157</v>
       </c>
       <c r="F29">
-        <v>-2.040743714864494</v>
+        <v>-1.63862932652353</v>
       </c>
       <c r="G29">
-        <v>-4.784540606935703</v>
+        <v>-5.606489474517032</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.287437908210455</v>
       </c>
       <c r="E30">
-        <v>-24.25174649264536</v>
+        <v>-25.0130146726528</v>
       </c>
       <c r="F30">
-        <v>-1.853846633077467</v>
+        <v>-1.884442383099867</v>
       </c>
       <c r="G30">
-        <v>-5.83870438082367</v>
+        <v>-5.316671075827075</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.382476969345678</v>
       </c>
       <c r="E31">
-        <v>-24.04949578651478</v>
+        <v>-24.63529918414702</v>
       </c>
       <c r="F31">
-        <v>-1.961051457245571</v>
+        <v>-1.758212444791667</v>
       </c>
       <c r="G31">
-        <v>-4.942589361526049</v>
+        <v>-5.527377367765068</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.258314022347276</v>
       </c>
       <c r="E32">
-        <v>-24.40210088664803</v>
+        <v>-24.39108310938737</v>
       </c>
       <c r="F32">
-        <v>-2.061593722392958</v>
+        <v>-2.054411777010686</v>
       </c>
       <c r="G32">
-        <v>-5.668390055010325</v>
+        <v>-5.428766147786797</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.925857286492842</v>
       </c>
       <c r="E33">
-        <v>-23.2456373084652</v>
+        <v>-23.83811114831074</v>
       </c>
       <c r="F33">
-        <v>-2.517548678446278</v>
+        <v>-1.906448791522638</v>
       </c>
       <c r="G33">
-        <v>-5.368305654603088</v>
+        <v>-6.230871605405735</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.413331001373444</v>
       </c>
       <c r="E34">
-        <v>-23.41735704283606</v>
+        <v>-23.95044900301902</v>
       </c>
       <c r="F34">
-        <v>-2.269431103755354</v>
+        <v>-1.925770461192937</v>
       </c>
       <c r="G34">
-        <v>-5.406340512303775</v>
+        <v>-5.85405538048927</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.757898370780643</v>
       </c>
       <c r="E35">
-        <v>-23.42626455120915</v>
+        <v>-23.99037202987064</v>
       </c>
       <c r="F35">
-        <v>-2.084666239663132</v>
+        <v>-1.964301142566753</v>
       </c>
       <c r="G35">
-        <v>-5.877229199264169</v>
+        <v>-5.347651160983575</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.005764883284629</v>
       </c>
       <c r="E36">
-        <v>-22.4299006430935</v>
+        <v>-23.66679897660057</v>
       </c>
       <c r="F36">
-        <v>-2.339166385192627</v>
+        <v>-2.117407461258783</v>
       </c>
       <c r="G36">
-        <v>-5.014338814998673</v>
+        <v>-4.851307689371724</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.20281687417641</v>
       </c>
       <c r="E37">
-        <v>-21.99684267373999</v>
+        <v>-22.49929950726105</v>
       </c>
       <c r="F37">
-        <v>-2.599923189715467</v>
+        <v>-2.387506593350395</v>
       </c>
       <c r="G37">
-        <v>-4.275732931368497</v>
+        <v>-4.919134146380312</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.395452132469754</v>
       </c>
       <c r="E38">
-        <v>-22.9764783988713</v>
+        <v>-22.38441665016046</v>
       </c>
       <c r="F38">
-        <v>-2.496601751931687</v>
+        <v>-2.366427956418759</v>
       </c>
       <c r="G38">
-        <v>-4.06167636734476</v>
+        <v>-4.098406870102974</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.622092839584103</v>
       </c>
       <c r="E39">
-        <v>-20.78389091078548</v>
+        <v>-21.82343381856426</v>
       </c>
       <c r="F39">
-        <v>-2.845088462982814</v>
+        <v>-2.418235710524646</v>
       </c>
       <c r="G39">
-        <v>-3.192668094922692</v>
+        <v>-4.20044781525993</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.918348801235442</v>
       </c>
       <c r="E40">
-        <v>-20.6182393315849</v>
+        <v>-20.64477618926985</v>
       </c>
       <c r="F40">
-        <v>-2.897499268557939</v>
+        <v>-2.301790447978314</v>
       </c>
       <c r="G40">
-        <v>-3.16746822227776</v>
+        <v>-3.653224569255021</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.310056898852164</v>
       </c>
       <c r="E41">
-        <v>-21.17574429514321</v>
+        <v>-20.87596384430944</v>
       </c>
       <c r="F41">
-        <v>-3.031941641297493</v>
+        <v>-2.814362659278175</v>
       </c>
       <c r="G41">
-        <v>-3.031904692990144</v>
+        <v>-3.107971097845978</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.8188757166943069</v>
       </c>
       <c r="E42">
-        <v>-19.68827190936972</v>
+        <v>-20.00796406041521</v>
       </c>
       <c r="F42">
-        <v>-3.261919626601914</v>
+        <v>-3.056068670271431</v>
       </c>
       <c r="G42">
-        <v>-2.548406138070666</v>
+        <v>-4.285204402156351</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.4540687983296057</v>
       </c>
       <c r="E43">
-        <v>-18.77136460619265</v>
+        <v>-19.91318309943467</v>
       </c>
       <c r="F43">
-        <v>-3.702523277946554</v>
+        <v>-2.82007508088788</v>
       </c>
       <c r="G43">
-        <v>-2.476504399503234</v>
+        <v>-3.172503562042991</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.2179396031932093</v>
       </c>
       <c r="E44">
-        <v>-19.27243572666737</v>
+        <v>-20.4637911970793</v>
       </c>
       <c r="F44">
-        <v>-3.527832189839778</v>
+        <v>-3.018719240814007</v>
       </c>
       <c r="G44">
-        <v>-2.65108932906224</v>
+        <v>-2.969438009209636</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.1015904716937829</v>
       </c>
       <c r="E45">
-        <v>-18.20582160127073</v>
+        <v>-19.27325085198875</v>
       </c>
       <c r="F45">
-        <v>-3.611505581196556</v>
+        <v>-3.147445878474245</v>
       </c>
       <c r="G45">
-        <v>-2.003847881224869</v>
+        <v>-2.475411919475275</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.09133523027780972</v>
       </c>
       <c r="E46">
-        <v>-18.06352789100172</v>
+        <v>-18.13026854092676</v>
       </c>
       <c r="F46">
-        <v>-3.436779701658862</v>
+        <v>-3.145527379569361</v>
       </c>
       <c r="G46">
-        <v>-2.437039386129582</v>
+        <v>-3.499489455502345</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.1658505346014053</v>
       </c>
       <c r="E47">
-        <v>-17.55520215516671</v>
+        <v>-18.10607290430378</v>
       </c>
       <c r="F47">
-        <v>-3.766691930437015</v>
+        <v>-3.628770414605703</v>
       </c>
       <c r="G47">
-        <v>-2.472485397218559</v>
+        <v>-3.530757558120762</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.3010215398933945</v>
       </c>
       <c r="E48">
-        <v>-16.64560380903803</v>
+        <v>-17.3172127321676</v>
       </c>
       <c r="F48">
-        <v>-4.317854465563695</v>
+        <v>-3.181571301999973</v>
       </c>
       <c r="G48">
-        <v>-1.929251358588472</v>
+        <v>-3.097218445934425</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.4697807187142655</v>
       </c>
       <c r="E49">
-        <v>-17.16568546339694</v>
+        <v>-17.38065212454105</v>
       </c>
       <c r="F49">
-        <v>-4.190174055933192</v>
+        <v>-3.537572133761894</v>
       </c>
       <c r="G49">
-        <v>-2.327814557152408</v>
+        <v>-2.513165380805124</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.647434209970444</v>
       </c>
       <c r="E50">
-        <v>-16.24533199150004</v>
+        <v>-16.60592079130881</v>
       </c>
       <c r="F50">
-        <v>-3.994807745819943</v>
+        <v>-3.650389975451367</v>
       </c>
       <c r="G50">
-        <v>-2.178621511879613</v>
+        <v>-2.897864014650593</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.8128876531945547</v>
       </c>
       <c r="E51">
-        <v>-15.48127427150388</v>
+        <v>-15.58653864981217</v>
       </c>
       <c r="F51">
-        <v>-4.006747005196493</v>
+        <v>-3.392095907217051</v>
       </c>
       <c r="G51">
-        <v>-1.879417716585822</v>
+        <v>-3.06507966983918</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.9505181786910837</v>
       </c>
       <c r="E52">
-        <v>-15.01307534385084</v>
+        <v>-15.66541561007778</v>
       </c>
       <c r="F52">
-        <v>-4.363377396184541</v>
+        <v>-3.568920041386036</v>
       </c>
       <c r="G52">
-        <v>-2.249977010433064</v>
+        <v>-2.899138574683212</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.050081120848791</v>
       </c>
       <c r="E53">
-        <v>-14.3751401534423</v>
+        <v>-15.62681036916239</v>
       </c>
       <c r="F53">
-        <v>-4.212964099919013</v>
+        <v>-3.640248273338893</v>
       </c>
       <c r="G53">
-        <v>-2.360228108527413</v>
+        <v>-2.88115900185943</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.108064614286117</v>
       </c>
       <c r="E54">
-        <v>-13.92074854303865</v>
+        <v>-14.30413820947604</v>
       </c>
       <c r="F54">
-        <v>-4.286219114450781</v>
+        <v>-3.5724306624391</v>
       </c>
       <c r="G54">
-        <v>-2.482863957484174</v>
+        <v>-3.190887021422564</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.126950034308662</v>
       </c>
       <c r="E55">
-        <v>-13.64440294519457</v>
+        <v>-14.03611594685806</v>
       </c>
       <c r="F55">
-        <v>-4.177268920164979</v>
+        <v>-3.75745232042619</v>
       </c>
       <c r="G55">
-        <v>-2.593154782124994</v>
+        <v>-3.228799388938298</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.114398874315973</v>
       </c>
       <c r="E56">
-        <v>-12.80111504396021</v>
+        <v>-14.29969577647451</v>
       </c>
       <c r="F56">
-        <v>-4.292202412201202</v>
+        <v>-3.942715861694896</v>
       </c>
       <c r="G56">
-        <v>-2.554514094590621</v>
+        <v>-3.242488494743184</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.08166886439515</v>
       </c>
       <c r="E57">
-        <v>-12.20355119933005</v>
+        <v>-12.74362153795882</v>
       </c>
       <c r="F57">
-        <v>-4.514198249212247</v>
+        <v>-3.714708562441735</v>
       </c>
       <c r="G57">
-        <v>-2.391509453327986</v>
+        <v>-4.199745979605605</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.042223617873025</v>
       </c>
       <c r="E58">
-        <v>-11.95160954791331</v>
+        <v>-13.12616890823078</v>
       </c>
       <c r="F58">
-        <v>-4.323103001427832</v>
+        <v>-3.739789042296296</v>
       </c>
       <c r="G58">
-        <v>-2.272531757192119</v>
+        <v>-4.064887596517853</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.01071812235597</v>
       </c>
       <c r="E59">
-        <v>-11.62316838508499</v>
+        <v>-12.90597185960781</v>
       </c>
       <c r="F59">
-        <v>-4.519646421620459</v>
+        <v>-3.732854778767461</v>
       </c>
       <c r="G59">
-        <v>-2.891752747585098</v>
+        <v>-4.267155307876244</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.000785675701935</v>
       </c>
       <c r="E60">
-        <v>-11.38913231989458</v>
+        <v>-12.32888124596633</v>
       </c>
       <c r="F60">
-        <v>-4.232921127387258</v>
+        <v>-4.020904632477738</v>
       </c>
       <c r="G60">
-        <v>-3.18295495431047</v>
+        <v>-3.697277998746102</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.025238270095958</v>
       </c>
       <c r="E61">
-        <v>-10.64435684222308</v>
+        <v>-11.69345935863205</v>
       </c>
       <c r="F61">
-        <v>-4.275480159440889</v>
+        <v>-3.82550601603578</v>
       </c>
       <c r="G61">
-        <v>-3.868529208947062</v>
+        <v>-4.224015588954002</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.092370628937976</v>
       </c>
       <c r="E62">
-        <v>-9.893332070420986</v>
+        <v>-11.29129916743287</v>
       </c>
       <c r="F62">
-        <v>-4.594254988488403</v>
+        <v>-3.789337838494748</v>
       </c>
       <c r="G62">
-        <v>-3.658336051567656</v>
+        <v>-4.632354828495406</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.207575352465233</v>
       </c>
       <c r="E63">
-        <v>-9.629625443532317</v>
+        <v>-10.80931556490049</v>
       </c>
       <c r="F63">
-        <v>-4.344467425113434</v>
+        <v>-4.175976667016612</v>
       </c>
       <c r="G63">
-        <v>-4.053125228216823</v>
+        <v>-4.172337973085979</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.370929760754952</v>
       </c>
       <c r="E64">
-        <v>-8.961639299608878</v>
+        <v>-11.16053495198738</v>
       </c>
       <c r="F64">
-        <v>-4.672700553166113</v>
+        <v>-4.145581381905689</v>
       </c>
       <c r="G64">
-        <v>-4.726986772735473</v>
+        <v>-4.721441608957194</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.580160162419427</v>
       </c>
       <c r="E65">
-        <v>-8.805049196897645</v>
+        <v>-10.92816083675778</v>
       </c>
       <c r="F65">
-        <v>-4.747594906788022</v>
+        <v>-4.102661181664438</v>
       </c>
       <c r="G65">
-        <v>-4.475292616475763</v>
+        <v>-4.592538897294592</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.827154091063543</v>
       </c>
       <c r="E66">
-        <v>-9.31044048157568</v>
+        <v>-10.52732748844285</v>
       </c>
       <c r="F66">
-        <v>-5.066313406852146</v>
+        <v>-4.172429597797825</v>
       </c>
       <c r="G66">
-        <v>-4.357715281103008</v>
+        <v>-4.936107313360155</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.102444570196574</v>
       </c>
       <c r="E67">
-        <v>-8.846951166890619</v>
+        <v>-10.21137132845368</v>
       </c>
       <c r="F67">
-        <v>-4.954733146062455</v>
+        <v>-4.37047567645913</v>
       </c>
       <c r="G67">
-        <v>-4.909007187575682</v>
+        <v>-4.75280240685071</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.391832278827991</v>
       </c>
       <c r="E68">
-        <v>-8.808051575164731</v>
+        <v>-10.66764678404452</v>
       </c>
       <c r="F68">
-        <v>-4.966968960969207</v>
+        <v>-4.228626042403743</v>
       </c>
       <c r="G68">
-        <v>-4.647838249982578</v>
+        <v>-5.510705460429299</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.681821802631894</v>
       </c>
       <c r="E69">
-        <v>-9.589697888206688</v>
+        <v>-10.40855467216967</v>
       </c>
       <c r="F69">
-        <v>-5.081965408928042</v>
+        <v>-4.250306074069812</v>
       </c>
       <c r="G69">
-        <v>-4.979064952277739</v>
+        <v>-4.78977457943329</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.956150404916414</v>
       </c>
       <c r="E70">
-        <v>-9.177135792211889</v>
+        <v>-10.98543244753279</v>
       </c>
       <c r="F70">
-        <v>-4.979792088364543</v>
+        <v>-4.460590452740077</v>
       </c>
       <c r="G70">
-        <v>-4.385364957447001</v>
+        <v>-5.056650897536098</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.202596733849898</v>
       </c>
       <c r="E71">
-        <v>-9.090039651622364</v>
+        <v>-10.30173702727675</v>
       </c>
       <c r="F71">
-        <v>-5.29315850663918</v>
+        <v>-4.602159270245916</v>
       </c>
       <c r="G71">
-        <v>-4.513681702549152</v>
+        <v>-4.85546242402351</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.408917751351166</v>
       </c>
       <c r="E72">
-        <v>-9.66180930830483</v>
+        <v>-10.43504624511455</v>
       </c>
       <c r="F72">
-        <v>-5.252872514738831</v>
+        <v>-4.361568241776827</v>
       </c>
       <c r="G72">
-        <v>-4.916032165210015</v>
+        <v>-4.47262762731665</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.570404095222886</v>
       </c>
       <c r="E73">
-        <v>-9.240317061566905</v>
+        <v>-10.12639904217376</v>
       </c>
       <c r="F73">
-        <v>-5.00687473223167</v>
+        <v>-4.529312640843727</v>
       </c>
       <c r="G73">
-        <v>-5.027124141871338</v>
+        <v>-4.142003444309637</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.683626289447731</v>
       </c>
       <c r="E74">
-        <v>-9.795458161693206</v>
+        <v>-10.61028460378937</v>
       </c>
       <c r="F74">
-        <v>-5.332189521924287</v>
+        <v>-4.504801249394889</v>
       </c>
       <c r="G74">
-        <v>-4.680185590446796</v>
+        <v>-4.616871407008235</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.753684085243316</v>
       </c>
       <c r="E75">
-        <v>-9.804234344320072</v>
+        <v>-10.61799206655042</v>
       </c>
       <c r="F75">
-        <v>-4.813768208393258</v>
+        <v>-4.798874990858326</v>
       </c>
       <c r="G75">
-        <v>-3.576241143284808</v>
+        <v>-4.405450037233759</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.784707587055492</v>
       </c>
       <c r="E76">
-        <v>-9.833008268164809</v>
+        <v>-10.53881622700031</v>
       </c>
       <c r="F76">
-        <v>-5.434003331034971</v>
+        <v>-4.813833649418079</v>
       </c>
       <c r="G76">
-        <v>-3.861053997119388</v>
+        <v>-4.092490925224297</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.788099084136443</v>
       </c>
       <c r="E77">
-        <v>-9.860876497208013</v>
+        <v>-11.05984433242683</v>
       </c>
       <c r="F77">
-        <v>-5.250808223171054</v>
+        <v>-4.776732730181495</v>
       </c>
       <c r="G77">
-        <v>-3.628100839157492</v>
+        <v>-3.771761962834165</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.771076780253455</v>
       </c>
       <c r="E78">
-        <v>-11.18549137224365</v>
+        <v>-11.46828551707465</v>
       </c>
       <c r="F78">
-        <v>-5.206608195292478</v>
+        <v>-5.149038317532718</v>
       </c>
       <c r="G78">
-        <v>-3.209181096072577</v>
+        <v>-3.186477374764255</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.747245463434226</v>
       </c>
       <c r="E79">
-        <v>-11.97723618232272</v>
+        <v>-12.1497393426969</v>
       </c>
       <c r="F79">
-        <v>-5.466428116282752</v>
+        <v>-5.327498477322233</v>
       </c>
       <c r="G79">
-        <v>-3.541311577299958</v>
+        <v>-4.00794621324239</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.722638383213654</v>
       </c>
       <c r="E80">
-        <v>-11.22247994793831</v>
+        <v>-12.85398497799976</v>
       </c>
       <c r="F80">
-        <v>-5.735910943026681</v>
+        <v>-5.337319601249823</v>
       </c>
       <c r="G80">
-        <v>-3.312996493638582</v>
+        <v>-3.484625106031018</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.708355791987725</v>
       </c>
       <c r="E81">
-        <v>-13.0001324196493</v>
+        <v>-13.33998080850294</v>
       </c>
       <c r="F81">
-        <v>-6.00803874688775</v>
+        <v>-4.992226711447966</v>
       </c>
       <c r="G81">
-        <v>-3.529214843899461</v>
+        <v>-3.148402790517097</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.705595432623287</v>
       </c>
       <c r="E82">
-        <v>-13.73075641604684</v>
+        <v>-14.80468855543987</v>
       </c>
       <c r="F82">
-        <v>-5.880322717458927</v>
+        <v>-5.392599043140843</v>
       </c>
       <c r="G82">
-        <v>-3.39585944848654</v>
+        <v>-3.44409740753926</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.721165330946273</v>
       </c>
       <c r="E83">
-        <v>-14.36311705495194</v>
+        <v>-15.47550952409211</v>
       </c>
       <c r="F83">
-        <v>-6.31381939067125</v>
+        <v>-5.339943869181893</v>
       </c>
       <c r="G83">
-        <v>-3.451076037536044</v>
+        <v>-3.01016434043375</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.751025022973973</v>
       </c>
       <c r="E84">
-        <v>-15.57045351013693</v>
+        <v>-16.57885863063897</v>
       </c>
       <c r="F84">
-        <v>-5.774613924820279</v>
+        <v>-5.762792293614928</v>
       </c>
       <c r="G84">
-        <v>-3.072409217663127</v>
+        <v>-2.407042532998247</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.798326689669894</v>
       </c>
       <c r="E85">
-        <v>-16.92482498787697</v>
+        <v>-17.48557686729878</v>
       </c>
       <c r="F85">
-        <v>-6.570811679532066</v>
+        <v>-5.463745034265084</v>
       </c>
       <c r="G85">
-        <v>-2.970209366320286</v>
+        <v>-3.657117770809204</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.854663144020769</v>
       </c>
       <c r="E86">
-        <v>-17.29489188378379</v>
+        <v>-19.54672086883796</v>
       </c>
       <c r="F86">
-        <v>-6.421428043948218</v>
+        <v>-5.751334315699405</v>
       </c>
       <c r="G86">
-        <v>-2.630984386002246</v>
+        <v>-3.320372389100078</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.921644703286065</v>
       </c>
       <c r="E87">
-        <v>-19.41181762814946</v>
+        <v>-20.49648677941467</v>
       </c>
       <c r="F87">
-        <v>-6.432252320800599</v>
+        <v>-5.851759781042998</v>
       </c>
       <c r="G87">
-        <v>-3.038274182607701</v>
+        <v>-3.185129982729771</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.989618564118463</v>
       </c>
       <c r="E88">
-        <v>-19.9938442784593</v>
+        <v>-20.87662047304055</v>
       </c>
       <c r="F88">
-        <v>-6.424764293662992</v>
+        <v>-5.836895556367163</v>
       </c>
       <c r="G88">
-        <v>-2.969742579399249</v>
+        <v>-3.517584897420002</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.061696179297629</v>
       </c>
       <c r="E89">
-        <v>-22.51508576765179</v>
+        <v>-22.20571853734378</v>
       </c>
       <c r="F89">
-        <v>-6.448096504113945</v>
+        <v>-5.958548764774896</v>
       </c>
       <c r="G89">
-        <v>-3.742476876993772</v>
+        <v>-3.196269968469419</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.130253376239438</v>
       </c>
       <c r="E90">
-        <v>-23.86380570983026</v>
+        <v>-24.22953885611174</v>
       </c>
       <c r="F90">
-        <v>-6.700974706268759</v>
+        <v>-6.054747071262002</v>
       </c>
       <c r="G90">
-        <v>-2.761125241696536</v>
+        <v>-2.146979317615259</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.2032813146461</v>
       </c>
       <c r="E91">
-        <v>-26.00793852603401</v>
+        <v>-26.28910242022224</v>
       </c>
       <c r="F91">
-        <v>-6.45652224315152</v>
+        <v>-6.32419676330982</v>
       </c>
       <c r="G91">
-        <v>-3.610541705617198</v>
+        <v>-3.666086038675089</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.276700327912327</v>
       </c>
       <c r="E92">
-        <v>-26.93220912794754</v>
+        <v>-27.69707744479108</v>
       </c>
       <c r="F92">
-        <v>-6.880989711673328</v>
+        <v>-6.297238374553113</v>
       </c>
       <c r="G92">
-        <v>-3.830116949054898</v>
+        <v>-4.014229628675926</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.363999302035399</v>
       </c>
       <c r="E93">
-        <v>-30.06575011619115</v>
+        <v>-30.48346335136968</v>
       </c>
       <c r="F93">
-        <v>-6.583807107347186</v>
+        <v>-6.035096539732793</v>
       </c>
       <c r="G93">
-        <v>-4.140523630453583</v>
+        <v>-4.224273811506065</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.464461551631798</v>
       </c>
       <c r="E94">
-        <v>-32.41165814875467</v>
+        <v>-31.76323954101837</v>
       </c>
       <c r="F94">
-        <v>-6.760248535776078</v>
+        <v>-6.247236461385329</v>
       </c>
       <c r="G94">
-        <v>-5.113840571727008</v>
+        <v>-3.945837068380122</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.592985250289495</v>
       </c>
       <c r="E95">
-        <v>-34.84544574791103</v>
+        <v>-33.82245894110429</v>
       </c>
       <c r="F95">
-        <v>-6.732255101949572</v>
+        <v>-6.385724994703858</v>
       </c>
       <c r="G95">
-        <v>-5.139851528029062</v>
+        <v>-5.125576455663724</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.753994239626138</v>
       </c>
       <c r="E96">
-        <v>-35.98434790389211</v>
+        <v>-36.38109656865213</v>
       </c>
       <c r="F96">
-        <v>-6.819111495051607</v>
+        <v>-6.487954230067046</v>
       </c>
       <c r="G96">
-        <v>-5.62348581531565</v>
+        <v>-5.561720967189467</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.956803440814483</v>
       </c>
       <c r="E97">
-        <v>-39.3970081803095</v>
+        <v>-39.17994257146283</v>
       </c>
       <c r="F97">
-        <v>-7.064126833819047</v>
+        <v>-6.828183774847068</v>
       </c>
       <c r="G97">
-        <v>-5.702647580250702</v>
+        <v>-5.38668911398266</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.213000506147</v>
       </c>
       <c r="E98">
-        <v>-41.55236255510425</v>
+        <v>-42.11556433896421</v>
       </c>
       <c r="F98">
-        <v>-6.831913499078172</v>
+        <v>-6.504177391467173</v>
       </c>
       <c r="G98">
-        <v>-6.145982596687743</v>
+        <v>-6.020062686556024</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.516686680022017</v>
       </c>
       <c r="E99">
-        <v>-44.39330298805325</v>
+        <v>-44.77945502363531</v>
       </c>
       <c r="F99">
-        <v>-6.929200280332557</v>
+        <v>-6.486814396520794</v>
       </c>
       <c r="G99">
-        <v>-7.022522360211654</v>
+        <v>-6.79914329994933</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.893905147383789</v>
       </c>
       <c r="E100">
-        <v>-46.21193814953367</v>
+        <v>-46.67713696315662</v>
       </c>
       <c r="F100">
-        <v>-6.910399239574918</v>
+        <v>-6.645479888853012</v>
       </c>
       <c r="G100">
-        <v>-8.214927894728508</v>
+        <v>-6.957178812357519</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.302228849391351</v>
       </c>
       <c r="E101">
-        <v>-49.36114199725131</v>
+        <v>-48.73766622434926</v>
       </c>
       <c r="F101">
-        <v>-6.562356533451692</v>
+        <v>-6.759566789403573</v>
       </c>
       <c r="G101">
-        <v>-8.140576352462014</v>
+        <v>-7.709602913068614</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.814174440560972</v>
       </c>
       <c r="E102">
-        <v>-50.99591318919079</v>
+        <v>-51.79813688812361</v>
       </c>
       <c r="F102">
-        <v>-6.769236736280154</v>
+        <v>-6.865489300832143</v>
       </c>
       <c r="G102">
-        <v>-8.966163509591004</v>
+        <v>-7.818840984227945</v>
       </c>
     </row>
   </sheetData>
